--- a/samples/현대카드_실제형식_예시.xlsx
+++ b/samples/현대카드_실제형식_예시.xlsx
@@ -779,7 +779,7 @@
         <v>129,660</v>
       </c>
       <c r="E15" t="str">
-        <v>109,330</v>
+        <v>115,330</v>
       </c>
       <c r="F15" t="str">
         <v/>
